--- a/public/fixtures/edge_healthcare.xlsx
+++ b/public/fixtures/edge_healthcare.xlsx
@@ -53946,7 +53946,7 @@
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>53507</t>
+          <t>53920</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -54215,7 +54215,7 @@
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>10463</t>
+          <t>12009</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
@@ -54484,7 +54484,7 @@
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>77031</t>
+          <t>75751</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -54753,7 +54753,7 @@
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>33034</t>
+          <t>32044</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
@@ -55022,7 +55022,7 @@
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>85120</t>
+          <t>84531</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">

--- a/public/fixtures/edge_healthcare.xlsx
+++ b/public/fixtures/edge_healthcare.xlsx
@@ -53931,7 +53931,7 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>05/10/1990</t>
+          <t>01/01/1986</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -53976,7 +53976,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>03/02/2020</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54004,12 +54004,12 @@
       <c r="R18" s="14" t="n"/>
       <c r="S18" s="14" t="inlineStr">
         <is>
-          <t>$10.82</t>
+          <t>$10.38</t>
         </is>
       </c>
       <c r="T18" s="13" t="inlineStr">
         <is>
-          <t>$16.23</t>
+          <t>$15.57</t>
         </is>
       </c>
       <c r="U18" s="11" t="inlineStr">
@@ -54045,12 +54045,12 @@
       <c r="AA18" s="11" t="n"/>
       <c r="AB18" s="11" t="inlineStr">
         <is>
-          <t>$10.48</t>
+          <t>$10.05</t>
         </is>
       </c>
       <c r="AC18" s="11" t="inlineStr">
         <is>
-          <t>$15.72</t>
+          <t>$15.08</t>
         </is>
       </c>
       <c r="AD18" s="11" t="inlineStr">
@@ -54070,18 +54070,18 @@
       </c>
       <c r="AG18" s="11" t="inlineStr">
         <is>
-          <t>$22,700.00</t>
+          <t>$21,800.00</t>
         </is>
       </c>
       <c r="AH18" s="11" t="n"/>
       <c r="AI18" s="11" t="inlineStr">
         <is>
-          <t>$10.19</t>
+          <t>$9.81</t>
         </is>
       </c>
       <c r="AJ18" s="11" t="inlineStr">
         <is>
-          <t>$15.29</t>
+          <t>$14.71</t>
         </is>
       </c>
       <c r="AK18" s="11" t="inlineStr">
@@ -54101,18 +54101,18 @@
       </c>
       <c r="AN18" s="11" t="inlineStr">
         <is>
-          <t>$22,000.00</t>
+          <t>$21,200.00</t>
         </is>
       </c>
       <c r="AO18" s="11" t="n"/>
       <c r="AP18" s="11" t="inlineStr">
         <is>
-          <t>$9.90</t>
+          <t>$9.52</t>
         </is>
       </c>
       <c r="AQ18" s="11" t="inlineStr">
         <is>
-          <t>$14.85</t>
+          <t>$14.28</t>
         </is>
       </c>
       <c r="AR18" s="11" t="inlineStr">
@@ -54132,7 +54132,7 @@
       </c>
       <c r="AU18" s="11" t="inlineStr">
         <is>
-          <t>$21,400.00</t>
+          <t>$20,600.00</t>
         </is>
       </c>
       <c r="AV18" s="11" t="inlineStr">
@@ -54200,7 +54200,7 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>05/10/1990</t>
+          <t>01/25/1994</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -54245,7 +54245,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>03/02/2020</t>
+          <t>04/09/2024</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54273,12 +54273,12 @@
       <c r="R19" s="14" t="n"/>
       <c r="S19" s="14" t="inlineStr">
         <is>
-          <t>$14.62</t>
+          <t>$14.04</t>
         </is>
       </c>
       <c r="T19" s="13" t="inlineStr">
         <is>
-          <t>$21.93</t>
+          <t>$21.06</t>
         </is>
       </c>
       <c r="U19" s="11" t="inlineStr">
@@ -54314,12 +54314,12 @@
       <c r="AA19" s="11" t="n"/>
       <c r="AB19" s="11" t="inlineStr">
         <is>
-          <t>$14.18</t>
+          <t>$13.61</t>
         </is>
       </c>
       <c r="AC19" s="11" t="inlineStr">
         <is>
-          <t>$21.27</t>
+          <t>$20.41</t>
         </is>
       </c>
       <c r="AD19" s="11" t="inlineStr">
@@ -54339,18 +54339,18 @@
       </c>
       <c r="AG19" s="11" t="inlineStr">
         <is>
-          <t>$30,700.00</t>
+          <t>$29,500.00</t>
         </is>
       </c>
       <c r="AH19" s="11" t="n"/>
       <c r="AI19" s="11" t="inlineStr">
         <is>
-          <t>$13.75</t>
+          <t>$13.22</t>
         </is>
       </c>
       <c r="AJ19" s="11" t="inlineStr">
         <is>
-          <t>$20.62</t>
+          <t>$19.83</t>
         </is>
       </c>
       <c r="AK19" s="11" t="inlineStr">
@@ -54370,18 +54370,18 @@
       </c>
       <c r="AN19" s="11" t="inlineStr">
         <is>
-          <t>$29,700.00</t>
+          <t>$28,600.00</t>
         </is>
       </c>
       <c r="AO19" s="11" t="n"/>
       <c r="AP19" s="11" t="inlineStr">
         <is>
-          <t>$13.37</t>
+          <t>$12.84</t>
         </is>
       </c>
       <c r="AQ19" s="11" t="inlineStr">
         <is>
-          <t>$20.05</t>
+          <t>$19.26</t>
         </is>
       </c>
       <c r="AR19" s="11" t="inlineStr">
@@ -54401,7 +54401,7 @@
       </c>
       <c r="AU19" s="11" t="inlineStr">
         <is>
-          <t>$28,900.00</t>
+          <t>$27,800.00</t>
         </is>
       </c>
       <c r="AV19" s="11" t="inlineStr">
@@ -54469,7 +54469,7 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>05/10/1990</t>
+          <t>03/03/2000</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -54514,7 +54514,7 @@
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>03/02/2020</t>
+          <t>01/01/2015</t>
         </is>
       </c>
       <c r="L20" s="14" t="n"/>
@@ -54542,12 +54542,12 @@
       <c r="R20" s="14" t="n"/>
       <c r="S20" s="14" t="inlineStr">
         <is>
-          <t>$65.67</t>
+          <t>$63.03</t>
         </is>
       </c>
       <c r="T20" s="13" t="inlineStr">
         <is>
-          <t>$98.50</t>
+          <t>$94.55</t>
         </is>
       </c>
       <c r="U20" s="11" t="inlineStr">
@@ -54583,12 +54583,12 @@
       <c r="AA20" s="11" t="n"/>
       <c r="AB20" s="11" t="inlineStr">
         <is>
-          <t>$63.75</t>
+          <t>$61.20</t>
         </is>
       </c>
       <c r="AC20" s="11" t="inlineStr">
         <is>
-          <t>$95.62</t>
+          <t>$91.80</t>
         </is>
       </c>
       <c r="AD20" s="11" t="inlineStr">
@@ -54608,18 +54608,18 @@
       </c>
       <c r="AG20" s="11" t="inlineStr">
         <is>
-          <t>$137,900.00</t>
+          <t>$132,600.00</t>
         </is>
       </c>
       <c r="AH20" s="11" t="n"/>
       <c r="AI20" s="11" t="inlineStr">
         <is>
-          <t>$61.88</t>
+          <t>$59.42</t>
         </is>
       </c>
       <c r="AJ20" s="11" t="inlineStr">
         <is>
-          <t>$92.82</t>
+          <t>$89.13</t>
         </is>
       </c>
       <c r="AK20" s="11" t="inlineStr">
@@ -54639,18 +54639,18 @@
       </c>
       <c r="AN20" s="11" t="inlineStr">
         <is>
-          <t>$133,800.00</t>
+          <t>$128,700.00</t>
         </is>
       </c>
       <c r="AO20" s="11" t="n"/>
       <c r="AP20" s="11" t="inlineStr">
         <is>
-          <t>$60.10</t>
+          <t>$57.69</t>
         </is>
       </c>
       <c r="AQ20" s="11" t="inlineStr">
         <is>
-          <t>$90.15</t>
+          <t>$86.53</t>
         </is>
       </c>
       <c r="AR20" s="11" t="inlineStr">
@@ -54670,7 +54670,7 @@
       </c>
       <c r="AU20" s="11" t="inlineStr">
         <is>
-          <t>$130,000.00</t>
+          <t>$125,000.00</t>
         </is>
       </c>
       <c r="AV20" s="11" t="inlineStr">
@@ -54738,12 +54738,12 @@
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>05/10/1990</t>
+          <t>02/18/1967</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -54783,7 +54783,7 @@
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>03/02/2020</t>
+          <t>11/25/2015</t>
         </is>
       </c>
       <c r="L21" s="14" t="n"/>
@@ -54811,12 +54811,12 @@
       <c r="R21" s="14" t="n"/>
       <c r="S21" s="14" t="inlineStr">
         <is>
-          <t>$15.67</t>
+          <t>$15.05</t>
         </is>
       </c>
       <c r="T21" s="13" t="inlineStr">
         <is>
-          <t>$23.50</t>
+          <t>$22.58</t>
         </is>
       </c>
       <c r="U21" s="11" t="inlineStr">
@@ -54852,12 +54852,12 @@
       <c r="AA21" s="11" t="n"/>
       <c r="AB21" s="11" t="inlineStr">
         <is>
-          <t>$15.24</t>
+          <t>$14.62</t>
         </is>
       </c>
       <c r="AC21" s="11" t="inlineStr">
         <is>
-          <t>$22.86</t>
+          <t>$21.93</t>
         </is>
       </c>
       <c r="AD21" s="11" t="inlineStr">
@@ -54877,18 +54877,18 @@
       </c>
       <c r="AG21" s="11" t="inlineStr">
         <is>
-          <t>$33,000.00</t>
+          <t>$31,700.00</t>
         </is>
       </c>
       <c r="AH21" s="11" t="n"/>
       <c r="AI21" s="11" t="inlineStr">
         <is>
-          <t>$14.81</t>
+          <t>$14.23</t>
         </is>
       </c>
       <c r="AJ21" s="11" t="inlineStr">
         <is>
-          <t>$22.21</t>
+          <t>$21.34</t>
         </is>
       </c>
       <c r="AK21" s="11" t="inlineStr">
@@ -54908,18 +54908,18 @@
       </c>
       <c r="AN21" s="11" t="inlineStr">
         <is>
-          <t>$32,000.00</t>
+          <t>$30,800.00</t>
         </is>
       </c>
       <c r="AO21" s="11" t="n"/>
       <c r="AP21" s="11" t="inlineStr">
         <is>
-          <t>$14.38</t>
+          <t>$13.80</t>
         </is>
       </c>
       <c r="AQ21" s="11" t="inlineStr">
         <is>
-          <t>$21.57</t>
+          <t>$20.70</t>
         </is>
       </c>
       <c r="AR21" s="11" t="inlineStr">
@@ -54939,7 +54939,7 @@
       </c>
       <c r="AU21" s="11" t="inlineStr">
         <is>
-          <t>$31,100.00</t>
+          <t>$29,900.00</t>
         </is>
       </c>
       <c r="AV21" s="11" t="inlineStr">
@@ -55007,7 +55007,7 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>05/10/1990</t>
+          <t>09/25/1966</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -55052,7 +55052,7 @@
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>03/02/2020</t>
+          <t>12/27/2015</t>
         </is>
       </c>
       <c r="L22" s="14" t="n"/>
@@ -55080,12 +55080,12 @@
       <c r="R22" s="14" t="n"/>
       <c r="S22" s="14" t="inlineStr">
         <is>
-          <t>$11.83</t>
+          <t>$11.35</t>
         </is>
       </c>
       <c r="T22" s="13" t="inlineStr">
         <is>
-          <t>$17.75</t>
+          <t>$17.02</t>
         </is>
       </c>
       <c r="U22" s="11" t="inlineStr">
@@ -55121,12 +55121,12 @@
       <c r="AA22" s="11" t="n"/>
       <c r="AB22" s="11" t="inlineStr">
         <is>
-          <t>$11.49</t>
+          <t>$11.01</t>
         </is>
       </c>
       <c r="AC22" s="11" t="inlineStr">
         <is>
-          <t>$17.23</t>
+          <t>$16.52</t>
         </is>
       </c>
       <c r="AD22" s="11" t="inlineStr">
@@ -55146,18 +55146,18 @@
       </c>
       <c r="AG22" s="11" t="inlineStr">
         <is>
-          <t>$24,900.00</t>
+          <t>$23,900.00</t>
         </is>
       </c>
       <c r="AH22" s="11" t="n"/>
       <c r="AI22" s="11" t="inlineStr">
         <is>
-          <t>$11.15</t>
+          <t>$10.72</t>
         </is>
       </c>
       <c r="AJ22" s="11" t="inlineStr">
         <is>
-          <t>$16.73</t>
+          <t>$16.08</t>
         </is>
       </c>
       <c r="AK22" s="11" t="inlineStr">
@@ -55177,18 +55177,18 @@
       </c>
       <c r="AN22" s="11" t="inlineStr">
         <is>
-          <t>$24,100.00</t>
+          <t>$23,200.00</t>
         </is>
       </c>
       <c r="AO22" s="11" t="n"/>
       <c r="AP22" s="11" t="inlineStr">
         <is>
-          <t>$10.82</t>
+          <t>$10.38</t>
         </is>
       </c>
       <c r="AQ22" s="11" t="inlineStr">
         <is>
-          <t>$16.23</t>
+          <t>$15.57</t>
         </is>
       </c>
       <c r="AR22" s="11" t="inlineStr">
@@ -55208,7 +55208,7 @@
       </c>
       <c r="AU22" s="11" t="inlineStr">
         <is>
-          <t>$23,400.00</t>
+          <t>$22,500.00</t>
         </is>
       </c>
       <c r="AV22" s="11" t="inlineStr">

--- a/public/fixtures/edge_healthcare.xlsx
+++ b/public/fixtures/edge_healthcare.xlsx
@@ -8,9 +8,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priority Census Template" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Census Definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROVENANCE" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
     <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
     <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
     <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
@@ -33,6 +33,7 @@
     <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId23"/>
     <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId24"/>
     <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId25"/>
+    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId26"/>
   </externalReferences>
   <definedNames>
     <definedName name="_____dc1" hidden="1">{#N/A,#N/A,FALSE,"COVER PAGE";#N/A,#N/A,FALSE,"HIGHLITES";#N/A,#N/A,FALSE,"INC STATE (1)";#N/A,#N/A,FALSE,"DPC BY DEPT";#N/A,#N/A,FALSE,"FIXED COSTS";#N/A,#N/A,FALSE,"PRODUCTION";#N/A,#N/A,FALSE,"SALES TRND";#N/A,#N/A,FALSE,"BALANCE SHEET";#N/A,#N/A,FALSE,"INVENTORY";#N/A,#N/A,FALSE,"MFG VAR";#N/A,#N/A,FALSE,"OVRHD SPND";#N/A,#N/A,FALSE,"ENERGY COSTS";#N/A,#N/A,FALSE,"MAINTENANCE";#N/A,#N/A,FALSE,"LABOR";#N/A,#N/A,FALSE,"ACTVSFORECAST"}</definedName>
@@ -53931,7 +53932,7 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>01/01/1986</t>
+          <t>09/25/1966</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -53976,7 +53977,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>12/27/2016</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54200,12 +54201,12 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>01/25/1994</t>
+          <t>06/22/1967</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -54245,7 +54246,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>04/09/2024</t>
+          <t>12/26/2014</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54469,12 +54470,12 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>03/03/2000</t>
+          <t>02/02/1987</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -54514,7 +54515,7 @@
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>01/01/2015</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="L20" s="14" t="n"/>
@@ -54738,12 +54739,12 @@
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>02/18/1967</t>
+          <t>01/05/1970</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -54783,7 +54784,7 @@
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>11/25/2015</t>
+          <t>09/21/2013</t>
         </is>
       </c>
       <c r="L21" s="14" t="n"/>
@@ -55007,12 +55008,12 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>09/25/1966</t>
+          <t>04/08/1989</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -55052,7 +55053,7 @@
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>12/27/2015</t>
+          <t>10/22/2019</t>
         </is>
       </c>
       <c r="L22" s="14" t="n"/>
@@ -62705,4 +62706,471 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nine Dean — simulated census: data provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>generated 2026-07-20 00:02 from the reference warehouse (public.ext_*)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>warehouse table</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>vintage</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>feeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MIT · Living Wage Calculator</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ext_mit_expense</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>301,824</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>mit:livingwage.mit.edu:2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Engine A basket components</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MIT · Living Wage Calculator</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ext_mit_living_wage</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>113,184</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>mit:livingwage.mit.edu:2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Engine A living-wage reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EPI · Family Budget Calculator</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ext_epi_cost</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>502,880</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>epi:2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Engine A basket (food, childcare, medical, housing, other)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EPI · Family Budget Calculator</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ext_epi_county</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3,143</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>epi:2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Engine A county coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ACS · B25064 median gross rent</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ext_acs</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3,222</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>acs:5y2023-B25064</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Engine A housing candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CNT · H+T Affordability Index</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ext_cnt</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3,144</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>cnt:2022</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Engine A transportation (override, not MAX)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BLS OEWS · state wages</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ext_bls_oews_state_wage</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>35,427</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>May2024</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>wages by state+SOC (p10/p25/median); prevailing-wage overlay</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>O*NET · SOC occupations</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ext_onet_soc_occupation</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1,016</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>O*NET 29.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>job titles and SOC codes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>O*NET · SOC alternate titles</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ext_onet_soc_alt_title</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>55,119</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>O*NET 29.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>title → SOC matching</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Census · ZCTA↔county crosswalk</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ext_census_zcta_county</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>23,355</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>census_zcta:2020</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>residence ZIP → county</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Census · county gazetteer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ext_census_county</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3,222</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>census_county:2024</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>county names / states</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A Better Balance · PSL statutes</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ext_abb_psl_law</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>abb:2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Engine B floors (cap / preempted / no-cap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>KFF · EHBS benchmarks</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ext_kff_ehbs_health_benchmarks</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>kff_ehbs:2025</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Engine C employer-contribution thresholds</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Peterson-KFF · OOP cost-sharing</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ext_peterson_kff_oop_costsharing</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>live scrape; page modified 2026-02-11</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Engine C out-of-pocket exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PolicyEngine US</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>in-process library (not a warehouse table)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>policyengine-us 1.745.0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Engine A federal + state + payroll + local tax</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/public/fixtures/edge_healthcare.xlsx
+++ b/public/fixtures/edge_healthcare.xlsx
@@ -53932,7 +53932,7 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>09/25/1966</t>
+          <t>05/05/1970</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -53977,7 +53977,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>12/27/2016</t>
+          <t>09/19/2014</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54201,12 +54201,12 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>06/22/1967</t>
+          <t>03/27/1980</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -54246,7 +54246,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>12/26/2014</t>
+          <t>07/20/2020</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54470,12 +54470,12 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>02/02/1987</t>
+          <t>07/27/1972</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -54515,7 +54515,7 @@
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>03/16/2024</t>
         </is>
       </c>
       <c r="L20" s="14" t="n"/>
@@ -54739,7 +54739,7 @@
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>01/05/1970</t>
+          <t>01/17/1966</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -54784,7 +54784,7 @@
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>09/21/2013</t>
+          <t>09/24/2021</t>
         </is>
       </c>
       <c r="L21" s="14" t="n"/>
@@ -55008,12 +55008,12 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>04/08/1989</t>
+          <t>11/11/2000</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -55053,7 +55053,7 @@
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>10/22/2019</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="L22" s="14" t="n"/>
@@ -62734,7 +62734,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-07-20 00:02 from the reference warehouse (public.ext_*)</t>
+          <t>generated 2026-07-20 00:26 from the reference warehouse (public.ext_*)</t>
         </is>
       </c>
     </row>

--- a/public/fixtures/edge_healthcare.xlsx
+++ b/public/fixtures/edge_healthcare.xlsx
@@ -53932,7 +53932,7 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>05/05/1970</t>
+          <t>03/19/1976</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -53977,7 +53977,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>09/19/2014</t>
+          <t>08/03/2022</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54246,7 +54246,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>07/20/2020</t>
+          <t>01/12/2014</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54470,7 +54470,7 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>07/27/1972</t>
+          <t>07/03/1996</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -54515,7 +54515,7 @@
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>03/16/2024</t>
+          <t>03/16/2018</t>
         </is>
       </c>
       <c r="L20" s="14" t="n"/>
@@ -54739,7 +54739,7 @@
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>01/17/1966</t>
+          <t>09/25/1962</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -54784,7 +54784,7 @@
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>09/24/2021</t>
+          <t>09/11/2018</t>
         </is>
       </c>
       <c r="L21" s="14" t="n"/>
@@ -55008,12 +55008,12 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>11/11/2000</t>
+          <t>02/22/1987</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -55053,7 +55053,7 @@
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/08/2017</t>
         </is>
       </c>
       <c r="L22" s="14" t="n"/>
@@ -62734,7 +62734,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-07-20 00:26 from the reference warehouse (public.ext_*)</t>
+          <t>generated 2026-07-20 12:56 from the reference warehouse (public.ext_*)</t>
         </is>
       </c>
     </row>

--- a/public/fixtures/edge_healthcare.xlsx
+++ b/public/fixtures/edge_healthcare.xlsx
@@ -53075,7 +53075,11 @@
           <t>Company Name:</t>
         </is>
       </c>
-      <c r="B8" s="46" t="n"/>
+      <c r="B8" s="46" t="inlineStr">
+        <is>
+          <t>Anvil Point Industrial Services, LLC</t>
+        </is>
+      </c>
       <c r="C8" s="46" t="n"/>
       <c r="D8" s="46" t="n"/>
       <c r="E8" s="45" t="n"/>
@@ -53140,7 +53144,11 @@
           <t>Date</t>
         </is>
       </c>
-      <c r="B9" s="43" t="n"/>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>07/20/2026</t>
+        </is>
+      </c>
       <c r="C9" s="43" t="n"/>
       <c r="D9" s="43" t="n"/>
       <c r="E9" s="43" t="n"/>
@@ -53932,12 +53940,12 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>03/19/1976</t>
+          <t>10/02/1991</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -53977,7 +53985,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>08/03/2022</t>
+          <t>04/17/2018</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54201,7 +54209,7 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>03/27/1980</t>
+          <t>05/09/1990</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -54246,7 +54254,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>01/12/2014</t>
+          <t>03/18/2014</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54470,7 +54478,7 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>07/03/1996</t>
+          <t>07/07/1980</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -54515,7 +54523,7 @@
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>03/16/2018</t>
+          <t>05/13/2020</t>
         </is>
       </c>
       <c r="L20" s="14" t="n"/>
@@ -54739,12 +54747,12 @@
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>09/25/1962</t>
+          <t>04/04/1989</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -54784,7 +54792,7 @@
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>09/11/2018</t>
+          <t>11/14/2018</t>
         </is>
       </c>
       <c r="L21" s="14" t="n"/>
@@ -55008,7 +55016,7 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>02/22/1987</t>
+          <t>06/02/1983</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -55053,7 +55061,7 @@
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>01/08/2017</t>
+          <t>05/23/2019</t>
         </is>
       </c>
       <c r="L22" s="14" t="n"/>
@@ -62734,7 +62742,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-07-20 12:56 from the reference warehouse (public.ext_*)</t>
+          <t>generated 2026-07-20 18:20 from the reference warehouse (public.ext_*)</t>
         </is>
       </c>
     </row>

--- a/public/fixtures/edge_healthcare.xlsx
+++ b/public/fixtures/edge_healthcare.xlsx
@@ -53940,12 +53940,12 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>10/02/1991</t>
+          <t>11/19/1992</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -53965,7 +53965,7 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>33-9011</t>
+          <t>29-1124</t>
         </is>
       </c>
       <c r="H18" s="14" t="inlineStr">
@@ -53975,7 +53975,7 @@
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>Animal Control Workers</t>
+          <t>Radiation Therapists</t>
         </is>
       </c>
       <c r="J18" s="14" t="inlineStr">
@@ -53985,7 +53985,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>04/17/2018</t>
+          <t>06/13/2020</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54013,12 +54013,12 @@
       <c r="R18" s="14" t="n"/>
       <c r="S18" s="14" t="inlineStr">
         <is>
-          <t>$10.38</t>
+          <t>$27.74</t>
         </is>
       </c>
       <c r="T18" s="13" t="inlineStr">
         <is>
-          <t>$15.57</t>
+          <t>$41.61</t>
         </is>
       </c>
       <c r="U18" s="11" t="inlineStr">
@@ -54038,7 +54038,7 @@
       </c>
       <c r="X18" s="11" t="inlineStr">
         <is>
-          <t>$900.00</t>
+          <t>$2,400.00</t>
         </is>
       </c>
       <c r="Y18" s="11" t="inlineStr">
@@ -54048,18 +54048,18 @@
       </c>
       <c r="Z18" s="11" t="inlineStr">
         <is>
-          <t>$22,500.00</t>
+          <t>$60,100.00</t>
         </is>
       </c>
       <c r="AA18" s="11" t="n"/>
       <c r="AB18" s="11" t="inlineStr">
         <is>
-          <t>$10.05</t>
+          <t>$26.92</t>
         </is>
       </c>
       <c r="AC18" s="11" t="inlineStr">
         <is>
-          <t>$15.08</t>
+          <t>$40.38</t>
         </is>
       </c>
       <c r="AD18" s="11" t="inlineStr">
@@ -54069,7 +54069,7 @@
       </c>
       <c r="AE18" s="11" t="inlineStr">
         <is>
-          <t>$900.00</t>
+          <t>$2,300.00</t>
         </is>
       </c>
       <c r="AF18" s="11" t="inlineStr">
@@ -54079,18 +54079,18 @@
       </c>
       <c r="AG18" s="11" t="inlineStr">
         <is>
-          <t>$21,800.00</t>
+          <t>$58,300.00</t>
         </is>
       </c>
       <c r="AH18" s="11" t="n"/>
       <c r="AI18" s="11" t="inlineStr">
         <is>
-          <t>$9.81</t>
+          <t>$26.11</t>
         </is>
       </c>
       <c r="AJ18" s="11" t="inlineStr">
         <is>
-          <t>$14.71</t>
+          <t>$39.16</t>
         </is>
       </c>
       <c r="AK18" s="11" t="inlineStr">
@@ -54100,7 +54100,7 @@
       </c>
       <c r="AL18" s="11" t="inlineStr">
         <is>
-          <t>$800.00</t>
+          <t>$2,300.00</t>
         </is>
       </c>
       <c r="AM18" s="11" t="inlineStr">
@@ -54110,18 +54110,18 @@
       </c>
       <c r="AN18" s="11" t="inlineStr">
         <is>
-          <t>$21,200.00</t>
+          <t>$56,600.00</t>
         </is>
       </c>
       <c r="AO18" s="11" t="n"/>
       <c r="AP18" s="11" t="inlineStr">
         <is>
-          <t>$9.52</t>
+          <t>$25.38</t>
         </is>
       </c>
       <c r="AQ18" s="11" t="inlineStr">
         <is>
-          <t>$14.28</t>
+          <t>$38.07</t>
         </is>
       </c>
       <c r="AR18" s="11" t="inlineStr">
@@ -54131,7 +54131,7 @@
       </c>
       <c r="AS18" s="11" t="inlineStr">
         <is>
-          <t>$800.00</t>
+          <t>$2,200.00</t>
         </is>
       </c>
       <c r="AT18" s="11" t="inlineStr">
@@ -54141,7 +54141,7 @@
       </c>
       <c r="AU18" s="11" t="inlineStr">
         <is>
-          <t>$20,600.00</t>
+          <t>$55,000.00</t>
         </is>
       </c>
       <c r="AV18" s="11" t="inlineStr">
@@ -54209,12 +54209,12 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>05/09/1990</t>
+          <t>02/26/1971</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -54234,7 +54234,7 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>49-3092</t>
+          <t>31-1132</t>
         </is>
       </c>
       <c r="H19" s="14" t="inlineStr">
@@ -54244,7 +54244,7 @@
       </c>
       <c r="I19" s="14" t="inlineStr">
         <is>
-          <t>Recreational Vehicle Service Technicians</t>
+          <t>Orderlies</t>
         </is>
       </c>
       <c r="J19" s="14" t="inlineStr">
@@ -54254,7 +54254,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>03/18/2014</t>
+          <t>06/06/2013</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54282,12 +54282,12 @@
       <c r="R19" s="14" t="n"/>
       <c r="S19" s="14" t="inlineStr">
         <is>
-          <t>$14.04</t>
+          <t>$13.27</t>
         </is>
       </c>
       <c r="T19" s="13" t="inlineStr">
         <is>
-          <t>$21.06</t>
+          <t>$19.91</t>
         </is>
       </c>
       <c r="U19" s="11" t="inlineStr">
@@ -54317,18 +54317,18 @@
       </c>
       <c r="Z19" s="11" t="inlineStr">
         <is>
-          <t>$30,400.00</t>
+          <t>$28,800.00</t>
         </is>
       </c>
       <c r="AA19" s="11" t="n"/>
       <c r="AB19" s="11" t="inlineStr">
         <is>
-          <t>$13.61</t>
+          <t>$12.93</t>
         </is>
       </c>
       <c r="AC19" s="11" t="inlineStr">
         <is>
-          <t>$20.41</t>
+          <t>$19.39</t>
         </is>
       </c>
       <c r="AD19" s="11" t="inlineStr">
@@ -54338,7 +54338,7 @@
       </c>
       <c r="AE19" s="11" t="inlineStr">
         <is>
-          <t>$1,200.00</t>
+          <t>$1,100.00</t>
         </is>
       </c>
       <c r="AF19" s="11" t="inlineStr">
@@ -54348,18 +54348,18 @@
       </c>
       <c r="AG19" s="11" t="inlineStr">
         <is>
-          <t>$29,500.00</t>
+          <t>$28,000.00</t>
         </is>
       </c>
       <c r="AH19" s="11" t="n"/>
       <c r="AI19" s="11" t="inlineStr">
         <is>
-          <t>$13.22</t>
+          <t>$12.55</t>
         </is>
       </c>
       <c r="AJ19" s="11" t="inlineStr">
         <is>
-          <t>$19.83</t>
+          <t>$18.83</t>
         </is>
       </c>
       <c r="AK19" s="11" t="inlineStr">
@@ -54379,18 +54379,18 @@
       </c>
       <c r="AN19" s="11" t="inlineStr">
         <is>
-          <t>$28,600.00</t>
+          <t>$27,200.00</t>
         </is>
       </c>
       <c r="AO19" s="11" t="n"/>
       <c r="AP19" s="11" t="inlineStr">
         <is>
-          <t>$12.84</t>
+          <t>$12.16</t>
         </is>
       </c>
       <c r="AQ19" s="11" t="inlineStr">
         <is>
-          <t>$19.26</t>
+          <t>$18.24</t>
         </is>
       </c>
       <c r="AR19" s="11" t="inlineStr">
@@ -54410,7 +54410,7 @@
       </c>
       <c r="AU19" s="11" t="inlineStr">
         <is>
-          <t>$27,800.00</t>
+          <t>$26,400.00</t>
         </is>
       </c>
       <c r="AV19" s="11" t="inlineStr">
@@ -54478,7 +54478,7 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>07/07/1980</t>
+          <t>11/07/1996</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -54503,7 +54503,7 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>29-1029</t>
+          <t>51-9011</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
@@ -54513,7 +54513,7 @@
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>Dentists, All Other Specialists</t>
+          <t>Chemical Equipment Operators and Tenders</t>
         </is>
       </c>
       <c r="J20" s="14" t="inlineStr">
@@ -54523,7 +54523,7 @@
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>05/13/2020</t>
+          <t>04/27/2022</t>
         </is>
       </c>
       <c r="L20" s="14" t="n"/>
@@ -54551,12 +54551,12 @@
       <c r="R20" s="14" t="n"/>
       <c r="S20" s="14" t="inlineStr">
         <is>
-          <t>$63.03</t>
+          <t>$13.22</t>
         </is>
       </c>
       <c r="T20" s="13" t="inlineStr">
         <is>
-          <t>$94.55</t>
+          <t>$19.83</t>
         </is>
       </c>
       <c r="U20" s="11" t="inlineStr">
@@ -54576,7 +54576,7 @@
       </c>
       <c r="X20" s="11" t="inlineStr">
         <is>
-          <t>$5,500.00</t>
+          <t>$1,100.00</t>
         </is>
       </c>
       <c r="Y20" s="11" t="inlineStr">
@@ -54586,18 +54586,18 @@
       </c>
       <c r="Z20" s="11" t="inlineStr">
         <is>
-          <t>$136,600.00</t>
+          <t>$28,600.00</t>
         </is>
       </c>
       <c r="AA20" s="11" t="n"/>
       <c r="AB20" s="11" t="inlineStr">
         <is>
-          <t>$61.20</t>
+          <t>$12.84</t>
         </is>
       </c>
       <c r="AC20" s="11" t="inlineStr">
         <is>
-          <t>$91.80</t>
+          <t>$19.26</t>
         </is>
       </c>
       <c r="AD20" s="11" t="inlineStr">
@@ -54607,7 +54607,7 @@
       </c>
       <c r="AE20" s="11" t="inlineStr">
         <is>
-          <t>$5,300.00</t>
+          <t>$1,100.00</t>
         </is>
       </c>
       <c r="AF20" s="11" t="inlineStr">
@@ -54617,18 +54617,18 @@
       </c>
       <c r="AG20" s="11" t="inlineStr">
         <is>
-          <t>$132,600.00</t>
+          <t>$27,800.00</t>
         </is>
       </c>
       <c r="AH20" s="11" t="n"/>
       <c r="AI20" s="11" t="inlineStr">
         <is>
-          <t>$59.42</t>
+          <t>$12.45</t>
         </is>
       </c>
       <c r="AJ20" s="11" t="inlineStr">
         <is>
-          <t>$89.13</t>
+          <t>$18.67</t>
         </is>
       </c>
       <c r="AK20" s="11" t="inlineStr">
@@ -54638,7 +54638,7 @@
       </c>
       <c r="AL20" s="11" t="inlineStr">
         <is>
-          <t>$5,100.00</t>
+          <t>$1,100.00</t>
         </is>
       </c>
       <c r="AM20" s="11" t="inlineStr">
@@ -54648,18 +54648,18 @@
       </c>
       <c r="AN20" s="11" t="inlineStr">
         <is>
-          <t>$128,700.00</t>
+          <t>$27,000.00</t>
         </is>
       </c>
       <c r="AO20" s="11" t="n"/>
       <c r="AP20" s="11" t="inlineStr">
         <is>
-          <t>$57.69</t>
+          <t>$12.12</t>
         </is>
       </c>
       <c r="AQ20" s="11" t="inlineStr">
         <is>
-          <t>$86.53</t>
+          <t>$18.18</t>
         </is>
       </c>
       <c r="AR20" s="11" t="inlineStr">
@@ -54669,7 +54669,7 @@
       </c>
       <c r="AS20" s="11" t="inlineStr">
         <is>
-          <t>$5,000.00</t>
+          <t>$1,000.00</t>
         </is>
       </c>
       <c r="AT20" s="11" t="inlineStr">
@@ -54679,7 +54679,7 @@
       </c>
       <c r="AU20" s="11" t="inlineStr">
         <is>
-          <t>$125,000.00</t>
+          <t>$26,200.00</t>
         </is>
       </c>
       <c r="AV20" s="11" t="inlineStr">
@@ -54747,12 +54747,12 @@
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>04/04/1989</t>
+          <t>07/27/1964</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -54772,7 +54772,7 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>33-3011</t>
+          <t>47-2061</t>
         </is>
       </c>
       <c r="H21" s="14" t="inlineStr">
@@ -54782,7 +54782,7 @@
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
-          <t>Bailiffs</t>
+          <t>Construction Laborers</t>
         </is>
       </c>
       <c r="J21" s="14" t="inlineStr">
@@ -54792,7 +54792,7 @@
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>11/14/2018</t>
+          <t>03/06/2020</t>
         </is>
       </c>
       <c r="L21" s="14" t="n"/>
@@ -54820,12 +54820,12 @@
       <c r="R21" s="14" t="n"/>
       <c r="S21" s="14" t="inlineStr">
         <is>
-          <t>$15.05</t>
+          <t>$11.63</t>
         </is>
       </c>
       <c r="T21" s="13" t="inlineStr">
         <is>
-          <t>$22.58</t>
+          <t>$17.45</t>
         </is>
       </c>
       <c r="U21" s="11" t="inlineStr">
@@ -54845,7 +54845,7 @@
       </c>
       <c r="X21" s="11" t="inlineStr">
         <is>
-          <t>$1,300.00</t>
+          <t>$1,000.00</t>
         </is>
       </c>
       <c r="Y21" s="11" t="inlineStr">
@@ -54855,18 +54855,18 @@
       </c>
       <c r="Z21" s="11" t="inlineStr">
         <is>
-          <t>$32,600.00</t>
+          <t>$25,200.00</t>
         </is>
       </c>
       <c r="AA21" s="11" t="n"/>
       <c r="AB21" s="11" t="inlineStr">
         <is>
-          <t>$14.62</t>
+          <t>$11.30</t>
         </is>
       </c>
       <c r="AC21" s="11" t="inlineStr">
         <is>
-          <t>$21.93</t>
+          <t>$16.95</t>
         </is>
       </c>
       <c r="AD21" s="11" t="inlineStr">
@@ -54876,7 +54876,7 @@
       </c>
       <c r="AE21" s="11" t="inlineStr">
         <is>
-          <t>$1,300.00</t>
+          <t>$1,000.00</t>
         </is>
       </c>
       <c r="AF21" s="11" t="inlineStr">
@@ -54886,18 +54886,18 @@
       </c>
       <c r="AG21" s="11" t="inlineStr">
         <is>
-          <t>$31,700.00</t>
+          <t>$24,500.00</t>
         </is>
       </c>
       <c r="AH21" s="11" t="n"/>
       <c r="AI21" s="11" t="inlineStr">
         <is>
-          <t>$14.23</t>
+          <t>$10.96</t>
         </is>
       </c>
       <c r="AJ21" s="11" t="inlineStr">
         <is>
-          <t>$21.34</t>
+          <t>$16.44</t>
         </is>
       </c>
       <c r="AK21" s="11" t="inlineStr">
@@ -54907,7 +54907,7 @@
       </c>
       <c r="AL21" s="11" t="inlineStr">
         <is>
-          <t>$1,200.00</t>
+          <t>$1,000.00</t>
         </is>
       </c>
       <c r="AM21" s="11" t="inlineStr">
@@ -54917,18 +54917,18 @@
       </c>
       <c r="AN21" s="11" t="inlineStr">
         <is>
-          <t>$30,800.00</t>
+          <t>$23,800.00</t>
         </is>
       </c>
       <c r="AO21" s="11" t="n"/>
       <c r="AP21" s="11" t="inlineStr">
         <is>
-          <t>$13.80</t>
+          <t>$10.67</t>
         </is>
       </c>
       <c r="AQ21" s="11" t="inlineStr">
         <is>
-          <t>$20.70</t>
+          <t>$16.00</t>
         </is>
       </c>
       <c r="AR21" s="11" t="inlineStr">
@@ -54938,7 +54938,7 @@
       </c>
       <c r="AS21" s="11" t="inlineStr">
         <is>
-          <t>$1,200.00</t>
+          <t>$900.00</t>
         </is>
       </c>
       <c r="AT21" s="11" t="inlineStr">
@@ -54948,7 +54948,7 @@
       </c>
       <c r="AU21" s="11" t="inlineStr">
         <is>
-          <t>$29,900.00</t>
+          <t>$23,100.00</t>
         </is>
       </c>
       <c r="AV21" s="11" t="inlineStr">
@@ -55016,7 +55016,7 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>06/02/1983</t>
+          <t>08/20/2001</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -55041,7 +55041,7 @@
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>53-7065</t>
+          <t>19-4092</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
@@ -55051,7 +55051,7 @@
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>Stockers and Order Fillers</t>
+          <t>Forensic Science Technicians</t>
         </is>
       </c>
       <c r="J22" s="14" t="inlineStr">
@@ -55061,7 +55061,7 @@
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>05/23/2019</t>
+          <t>05/07/2020</t>
         </is>
       </c>
       <c r="L22" s="14" t="n"/>
@@ -55089,12 +55089,12 @@
       <c r="R22" s="14" t="n"/>
       <c r="S22" s="14" t="inlineStr">
         <is>
-          <t>$11.35</t>
+          <t>$16.83</t>
         </is>
       </c>
       <c r="T22" s="13" t="inlineStr">
         <is>
-          <t>$17.02</t>
+          <t>$25.24</t>
         </is>
       </c>
       <c r="U22" s="11" t="inlineStr">
@@ -55114,7 +55114,7 @@
       </c>
       <c r="X22" s="11" t="inlineStr">
         <is>
-          <t>$1,000.00</t>
+          <t>$1,500.00</t>
         </is>
       </c>
       <c r="Y22" s="11" t="inlineStr">
@@ -55124,18 +55124,18 @@
       </c>
       <c r="Z22" s="11" t="inlineStr">
         <is>
-          <t>$24,600.00</t>
+          <t>$36,500.00</t>
         </is>
       </c>
       <c r="AA22" s="11" t="n"/>
       <c r="AB22" s="11" t="inlineStr">
         <is>
-          <t>$11.01</t>
+          <t>$16.35</t>
         </is>
       </c>
       <c r="AC22" s="11" t="inlineStr">
         <is>
-          <t>$16.52</t>
+          <t>$24.53</t>
         </is>
       </c>
       <c r="AD22" s="11" t="inlineStr">
@@ -55145,7 +55145,7 @@
       </c>
       <c r="AE22" s="11" t="inlineStr">
         <is>
-          <t>$1,000.00</t>
+          <t>$1,400.00</t>
         </is>
       </c>
       <c r="AF22" s="11" t="inlineStr">
@@ -55155,18 +55155,18 @@
       </c>
       <c r="AG22" s="11" t="inlineStr">
         <is>
-          <t>$23,900.00</t>
+          <t>$35,400.00</t>
         </is>
       </c>
       <c r="AH22" s="11" t="n"/>
       <c r="AI22" s="11" t="inlineStr">
         <is>
-          <t>$10.72</t>
+          <t>$15.87</t>
         </is>
       </c>
       <c r="AJ22" s="11" t="inlineStr">
         <is>
-          <t>$16.08</t>
+          <t>$23.80</t>
         </is>
       </c>
       <c r="AK22" s="11" t="inlineStr">
@@ -55176,7 +55176,7 @@
       </c>
       <c r="AL22" s="11" t="inlineStr">
         <is>
-          <t>$900.00</t>
+          <t>$1,400.00</t>
         </is>
       </c>
       <c r="AM22" s="11" t="inlineStr">
@@ -55186,18 +55186,18 @@
       </c>
       <c r="AN22" s="11" t="inlineStr">
         <is>
-          <t>$23,200.00</t>
+          <t>$34,400.00</t>
         </is>
       </c>
       <c r="AO22" s="11" t="n"/>
       <c r="AP22" s="11" t="inlineStr">
         <is>
-          <t>$10.38</t>
+          <t>$15.43</t>
         </is>
       </c>
       <c r="AQ22" s="11" t="inlineStr">
         <is>
-          <t>$15.57</t>
+          <t>$23.14</t>
         </is>
       </c>
       <c r="AR22" s="11" t="inlineStr">
@@ -55207,7 +55207,7 @@
       </c>
       <c r="AS22" s="11" t="inlineStr">
         <is>
-          <t>$900.00</t>
+          <t>$1,300.00</t>
         </is>
       </c>
       <c r="AT22" s="11" t="inlineStr">
@@ -55217,7 +55217,7 @@
       </c>
       <c r="AU22" s="11" t="inlineStr">
         <is>
-          <t>$22,500.00</t>
+          <t>$33,400.00</t>
         </is>
       </c>
       <c r="AV22" s="11" t="inlineStr">
@@ -62742,7 +62742,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-07-20 18:20 from the reference warehouse (public.ext_*)</t>
+          <t>generated 2026-07-20 19:47 from the reference warehouse (public.ext_*)</t>
         </is>
       </c>
     </row>

--- a/public/fixtures/edge_healthcare.xlsx
+++ b/public/fixtures/edge_healthcare.xlsx
@@ -53146,7 +53146,7 @@
       </c>
       <c r="B9" s="43" t="inlineStr">
         <is>
-          <t>07/20/2026</t>
+          <t>07/21/2026</t>
         </is>
       </c>
       <c r="C9" s="43" t="n"/>
@@ -53940,7 +53940,7 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>11/19/1992</t>
+          <t>07/23/1992</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -53965,7 +53965,7 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>29-1124</t>
+          <t>19-4021</t>
         </is>
       </c>
       <c r="H18" s="14" t="inlineStr">
@@ -53975,7 +53975,7 @@
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>Radiation Therapists</t>
+          <t>Biological Technicians</t>
         </is>
       </c>
       <c r="J18" s="14" t="inlineStr">
@@ -53985,7 +53985,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>06/13/2020</t>
+          <t>07/10/2020</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54013,12 +54013,12 @@
       <c r="R18" s="14" t="n"/>
       <c r="S18" s="14" t="inlineStr">
         <is>
-          <t>$27.74</t>
+          <t>$14.57</t>
         </is>
       </c>
       <c r="T18" s="13" t="inlineStr">
         <is>
-          <t>$41.61</t>
+          <t>$21.86</t>
         </is>
       </c>
       <c r="U18" s="11" t="inlineStr">
@@ -54038,7 +54038,7 @@
       </c>
       <c r="X18" s="11" t="inlineStr">
         <is>
-          <t>$2,400.00</t>
+          <t>$1,300.00</t>
         </is>
       </c>
       <c r="Y18" s="11" t="inlineStr">
@@ -54048,18 +54048,18 @@
       </c>
       <c r="Z18" s="11" t="inlineStr">
         <is>
-          <t>$60,100.00</t>
+          <t>$31,600.00</t>
         </is>
       </c>
       <c r="AA18" s="11" t="n"/>
       <c r="AB18" s="11" t="inlineStr">
         <is>
-          <t>$26.92</t>
+          <t>$14.18</t>
         </is>
       </c>
       <c r="AC18" s="11" t="inlineStr">
         <is>
-          <t>$40.38</t>
+          <t>$21.27</t>
         </is>
       </c>
       <c r="AD18" s="11" t="inlineStr">
@@ -54069,7 +54069,7 @@
       </c>
       <c r="AE18" s="11" t="inlineStr">
         <is>
-          <t>$2,300.00</t>
+          <t>$1,200.00</t>
         </is>
       </c>
       <c r="AF18" s="11" t="inlineStr">
@@ -54079,18 +54079,18 @@
       </c>
       <c r="AG18" s="11" t="inlineStr">
         <is>
-          <t>$58,300.00</t>
+          <t>$30,700.00</t>
         </is>
       </c>
       <c r="AH18" s="11" t="n"/>
       <c r="AI18" s="11" t="inlineStr">
         <is>
-          <t>$26.11</t>
+          <t>$13.75</t>
         </is>
       </c>
       <c r="AJ18" s="11" t="inlineStr">
         <is>
-          <t>$39.16</t>
+          <t>$20.62</t>
         </is>
       </c>
       <c r="AK18" s="11" t="inlineStr">
@@ -54100,7 +54100,7 @@
       </c>
       <c r="AL18" s="11" t="inlineStr">
         <is>
-          <t>$2,300.00</t>
+          <t>$1,200.00</t>
         </is>
       </c>
       <c r="AM18" s="11" t="inlineStr">
@@ -54110,18 +54110,18 @@
       </c>
       <c r="AN18" s="11" t="inlineStr">
         <is>
-          <t>$56,600.00</t>
+          <t>$29,800.00</t>
         </is>
       </c>
       <c r="AO18" s="11" t="n"/>
       <c r="AP18" s="11" t="inlineStr">
         <is>
-          <t>$25.38</t>
+          <t>$13.32</t>
         </is>
       </c>
       <c r="AQ18" s="11" t="inlineStr">
         <is>
-          <t>$38.07</t>
+          <t>$19.98</t>
         </is>
       </c>
       <c r="AR18" s="11" t="inlineStr">
@@ -54131,7 +54131,7 @@
       </c>
       <c r="AS18" s="11" t="inlineStr">
         <is>
-          <t>$2,200.00</t>
+          <t>$1,200.00</t>
         </is>
       </c>
       <c r="AT18" s="11" t="inlineStr">
@@ -54141,7 +54141,7 @@
       </c>
       <c r="AU18" s="11" t="inlineStr">
         <is>
-          <t>$55,000.00</t>
+          <t>$28,900.00</t>
         </is>
       </c>
       <c r="AV18" s="11" t="inlineStr">
@@ -54209,12 +54209,12 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>02/26/1971</t>
+          <t>01/09/1990</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -54234,7 +54234,7 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>31-1132</t>
+          <t>19-3039</t>
         </is>
       </c>
       <c r="H19" s="14" t="inlineStr">
@@ -54244,7 +54244,7 @@
       </c>
       <c r="I19" s="14" t="inlineStr">
         <is>
-          <t>Orderlies</t>
+          <t>Clinical Neuropsychologists</t>
         </is>
       </c>
       <c r="J19" s="14" t="inlineStr">
@@ -54254,7 +54254,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>06/06/2013</t>
+          <t>10/21/2012</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54282,12 +54282,12 @@
       <c r="R19" s="14" t="n"/>
       <c r="S19" s="14" t="inlineStr">
         <is>
-          <t>$13.27</t>
+          <t>$17.55</t>
         </is>
       </c>
       <c r="T19" s="13" t="inlineStr">
         <is>
-          <t>$19.91</t>
+          <t>$26.33</t>
         </is>
       </c>
       <c r="U19" s="11" t="inlineStr">
@@ -54307,7 +54307,7 @@
       </c>
       <c r="X19" s="11" t="inlineStr">
         <is>
-          <t>$1,200.00</t>
+          <t>$1,500.00</t>
         </is>
       </c>
       <c r="Y19" s="11" t="inlineStr">
@@ -54317,18 +54317,18 @@
       </c>
       <c r="Z19" s="11" t="inlineStr">
         <is>
-          <t>$28,800.00</t>
+          <t>$38,000.00</t>
         </is>
       </c>
       <c r="AA19" s="11" t="n"/>
       <c r="AB19" s="11" t="inlineStr">
         <is>
-          <t>$12.93</t>
+          <t>$17.02</t>
         </is>
       </c>
       <c r="AC19" s="11" t="inlineStr">
         <is>
-          <t>$19.39</t>
+          <t>$25.53</t>
         </is>
       </c>
       <c r="AD19" s="11" t="inlineStr">
@@ -54338,7 +54338,7 @@
       </c>
       <c r="AE19" s="11" t="inlineStr">
         <is>
-          <t>$1,100.00</t>
+          <t>$1,500.00</t>
         </is>
       </c>
       <c r="AF19" s="11" t="inlineStr">
@@ -54348,18 +54348,18 @@
       </c>
       <c r="AG19" s="11" t="inlineStr">
         <is>
-          <t>$28,000.00</t>
+          <t>$36,900.00</t>
         </is>
       </c>
       <c r="AH19" s="11" t="n"/>
       <c r="AI19" s="11" t="inlineStr">
         <is>
-          <t>$12.55</t>
+          <t>$16.54</t>
         </is>
       </c>
       <c r="AJ19" s="11" t="inlineStr">
         <is>
-          <t>$18.83</t>
+          <t>$24.81</t>
         </is>
       </c>
       <c r="AK19" s="11" t="inlineStr">
@@ -54369,7 +54369,7 @@
       </c>
       <c r="AL19" s="11" t="inlineStr">
         <is>
-          <t>$1,100.00</t>
+          <t>$1,400.00</t>
         </is>
       </c>
       <c r="AM19" s="11" t="inlineStr">
@@ -54379,18 +54379,18 @@
       </c>
       <c r="AN19" s="11" t="inlineStr">
         <is>
-          <t>$27,200.00</t>
+          <t>$35,800.00</t>
         </is>
       </c>
       <c r="AO19" s="11" t="n"/>
       <c r="AP19" s="11" t="inlineStr">
         <is>
-          <t>$12.16</t>
+          <t>$16.06</t>
         </is>
       </c>
       <c r="AQ19" s="11" t="inlineStr">
         <is>
-          <t>$18.24</t>
+          <t>$24.09</t>
         </is>
       </c>
       <c r="AR19" s="11" t="inlineStr">
@@ -54400,7 +54400,7 @@
       </c>
       <c r="AS19" s="11" t="inlineStr">
         <is>
-          <t>$1,100.00</t>
+          <t>$1,400.00</t>
         </is>
       </c>
       <c r="AT19" s="11" t="inlineStr">
@@ -54410,7 +54410,7 @@
       </c>
       <c r="AU19" s="11" t="inlineStr">
         <is>
-          <t>$26,400.00</t>
+          <t>$34,800.00</t>
         </is>
       </c>
       <c r="AV19" s="11" t="inlineStr">
@@ -54478,12 +54478,12 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>11/07/1996</t>
+          <t>08/20/1997</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -54503,7 +54503,7 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>51-9011</t>
+          <t>17-2121</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
@@ -54513,7 +54513,7 @@
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>Chemical Equipment Operators and Tenders</t>
+          <t>Marine Engineers and Naval Architects</t>
         </is>
       </c>
       <c r="J20" s="14" t="inlineStr">
@@ -54523,7 +54523,7 @@
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>04/27/2022</t>
+          <t>02/03/2020</t>
         </is>
       </c>
       <c r="L20" s="14" t="n"/>
@@ -54551,12 +54551,12 @@
       <c r="R20" s="14" t="n"/>
       <c r="S20" s="14" t="inlineStr">
         <is>
-          <t>$13.22</t>
+          <t>$32.07</t>
         </is>
       </c>
       <c r="T20" s="13" t="inlineStr">
         <is>
-          <t>$19.83</t>
+          <t>$48.11</t>
         </is>
       </c>
       <c r="U20" s="11" t="inlineStr">
@@ -54576,7 +54576,7 @@
       </c>
       <c r="X20" s="11" t="inlineStr">
         <is>
-          <t>$1,100.00</t>
+          <t>$2,800.00</t>
         </is>
       </c>
       <c r="Y20" s="11" t="inlineStr">
@@ -54586,18 +54586,18 @@
       </c>
       <c r="Z20" s="11" t="inlineStr">
         <is>
-          <t>$28,600.00</t>
+          <t>$69,500.00</t>
         </is>
       </c>
       <c r="AA20" s="11" t="n"/>
       <c r="AB20" s="11" t="inlineStr">
         <is>
-          <t>$12.84</t>
+          <t>$31.15</t>
         </is>
       </c>
       <c r="AC20" s="11" t="inlineStr">
         <is>
-          <t>$19.26</t>
+          <t>$46.72</t>
         </is>
       </c>
       <c r="AD20" s="11" t="inlineStr">
@@ -54607,7 +54607,7 @@
       </c>
       <c r="AE20" s="11" t="inlineStr">
         <is>
-          <t>$1,100.00</t>
+          <t>$2,700.00</t>
         </is>
       </c>
       <c r="AF20" s="11" t="inlineStr">
@@ -54617,18 +54617,18 @@
       </c>
       <c r="AG20" s="11" t="inlineStr">
         <is>
-          <t>$27,800.00</t>
+          <t>$67,500.00</t>
         </is>
       </c>
       <c r="AH20" s="11" t="n"/>
       <c r="AI20" s="11" t="inlineStr">
         <is>
-          <t>$12.45</t>
+          <t>$30.24</t>
         </is>
       </c>
       <c r="AJ20" s="11" t="inlineStr">
         <is>
-          <t>$18.67</t>
+          <t>$45.36</t>
         </is>
       </c>
       <c r="AK20" s="11" t="inlineStr">
@@ -54638,7 +54638,7 @@
       </c>
       <c r="AL20" s="11" t="inlineStr">
         <is>
-          <t>$1,100.00</t>
+          <t>$2,600.00</t>
         </is>
       </c>
       <c r="AM20" s="11" t="inlineStr">
@@ -54648,18 +54648,18 @@
       </c>
       <c r="AN20" s="11" t="inlineStr">
         <is>
-          <t>$27,000.00</t>
+          <t>$65,500.00</t>
         </is>
       </c>
       <c r="AO20" s="11" t="n"/>
       <c r="AP20" s="11" t="inlineStr">
         <is>
-          <t>$12.12</t>
+          <t>$29.38</t>
         </is>
       </c>
       <c r="AQ20" s="11" t="inlineStr">
         <is>
-          <t>$18.18</t>
+          <t>$44.07</t>
         </is>
       </c>
       <c r="AR20" s="11" t="inlineStr">
@@ -54669,7 +54669,7 @@
       </c>
       <c r="AS20" s="11" t="inlineStr">
         <is>
-          <t>$1,000.00</t>
+          <t>$2,500.00</t>
         </is>
       </c>
       <c r="AT20" s="11" t="inlineStr">
@@ -54679,7 +54679,7 @@
       </c>
       <c r="AU20" s="11" t="inlineStr">
         <is>
-          <t>$26,200.00</t>
+          <t>$63,600.00</t>
         </is>
       </c>
       <c r="AV20" s="11" t="inlineStr">
@@ -54747,12 +54747,12 @@
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>07/27/1964</t>
+          <t>10/06/1995</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -54772,7 +54772,7 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>47-2061</t>
+          <t>15-2041</t>
         </is>
       </c>
       <c r="H21" s="14" t="inlineStr">
@@ -54782,7 +54782,7 @@
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
-          <t>Construction Laborers</t>
+          <t>Biostatisticians</t>
         </is>
       </c>
       <c r="J21" s="14" t="inlineStr">
@@ -54792,7 +54792,7 @@
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>03/06/2020</t>
+          <t>09/21/2022</t>
         </is>
       </c>
       <c r="L21" s="14" t="n"/>
@@ -54820,12 +54820,12 @@
       <c r="R21" s="14" t="n"/>
       <c r="S21" s="14" t="inlineStr">
         <is>
-          <t>$11.63</t>
+          <t>$17.16</t>
         </is>
       </c>
       <c r="T21" s="13" t="inlineStr">
         <is>
-          <t>$17.45</t>
+          <t>$25.74</t>
         </is>
       </c>
       <c r="U21" s="11" t="inlineStr">
@@ -54845,7 +54845,7 @@
       </c>
       <c r="X21" s="11" t="inlineStr">
         <is>
-          <t>$1,000.00</t>
+          <t>$1,500.00</t>
         </is>
       </c>
       <c r="Y21" s="11" t="inlineStr">
@@ -54855,18 +54855,18 @@
       </c>
       <c r="Z21" s="11" t="inlineStr">
         <is>
-          <t>$25,200.00</t>
+          <t>$37,200.00</t>
         </is>
       </c>
       <c r="AA21" s="11" t="n"/>
       <c r="AB21" s="11" t="inlineStr">
         <is>
-          <t>$11.30</t>
+          <t>$16.68</t>
         </is>
       </c>
       <c r="AC21" s="11" t="inlineStr">
         <is>
-          <t>$16.95</t>
+          <t>$25.02</t>
         </is>
       </c>
       <c r="AD21" s="11" t="inlineStr">
@@ -54876,7 +54876,7 @@
       </c>
       <c r="AE21" s="11" t="inlineStr">
         <is>
-          <t>$1,000.00</t>
+          <t>$1,400.00</t>
         </is>
       </c>
       <c r="AF21" s="11" t="inlineStr">
@@ -54886,18 +54886,18 @@
       </c>
       <c r="AG21" s="11" t="inlineStr">
         <is>
-          <t>$24,500.00</t>
+          <t>$36,100.00</t>
         </is>
       </c>
       <c r="AH21" s="11" t="n"/>
       <c r="AI21" s="11" t="inlineStr">
         <is>
-          <t>$10.96</t>
+          <t>$16.15</t>
         </is>
       </c>
       <c r="AJ21" s="11" t="inlineStr">
         <is>
-          <t>$16.44</t>
+          <t>$24.22</t>
         </is>
       </c>
       <c r="AK21" s="11" t="inlineStr">
@@ -54907,7 +54907,7 @@
       </c>
       <c r="AL21" s="11" t="inlineStr">
         <is>
-          <t>$1,000.00</t>
+          <t>$1,400.00</t>
         </is>
       </c>
       <c r="AM21" s="11" t="inlineStr">
@@ -54917,18 +54917,18 @@
       </c>
       <c r="AN21" s="11" t="inlineStr">
         <is>
-          <t>$23,800.00</t>
+          <t>$35,000.00</t>
         </is>
       </c>
       <c r="AO21" s="11" t="n"/>
       <c r="AP21" s="11" t="inlineStr">
         <is>
-          <t>$10.67</t>
+          <t>$15.67</t>
         </is>
       </c>
       <c r="AQ21" s="11" t="inlineStr">
         <is>
-          <t>$16.00</t>
+          <t>$23.50</t>
         </is>
       </c>
       <c r="AR21" s="11" t="inlineStr">
@@ -54938,7 +54938,7 @@
       </c>
       <c r="AS21" s="11" t="inlineStr">
         <is>
-          <t>$900.00</t>
+          <t>$1,400.00</t>
         </is>
       </c>
       <c r="AT21" s="11" t="inlineStr">
@@ -54948,7 +54948,7 @@
       </c>
       <c r="AU21" s="11" t="inlineStr">
         <is>
-          <t>$23,100.00</t>
+          <t>$34,000.00</t>
         </is>
       </c>
       <c r="AV21" s="11" t="inlineStr">
@@ -55016,12 +55016,12 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>08/20/2001</t>
+          <t>11/19/2000</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -55041,7 +55041,7 @@
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>19-4092</t>
+          <t>11-9179</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
@@ -55051,7 +55051,7 @@
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>Forensic Science Technicians</t>
+          <t>Personal Service Managers, All Other</t>
         </is>
       </c>
       <c r="J22" s="14" t="inlineStr">
@@ -55061,7 +55061,7 @@
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>05/07/2020</t>
+          <t>06/05/2019</t>
         </is>
       </c>
       <c r="L22" s="14" t="n"/>
@@ -55089,12 +55089,12 @@
       <c r="R22" s="14" t="n"/>
       <c r="S22" s="14" t="inlineStr">
         <is>
-          <t>$16.83</t>
+          <t>$21.11</t>
         </is>
       </c>
       <c r="T22" s="13" t="inlineStr">
         <is>
-          <t>$25.24</t>
+          <t>$31.66</t>
         </is>
       </c>
       <c r="U22" s="11" t="inlineStr">
@@ -55114,7 +55114,7 @@
       </c>
       <c r="X22" s="11" t="inlineStr">
         <is>
-          <t>$1,500.00</t>
+          <t>$1,800.00</t>
         </is>
       </c>
       <c r="Y22" s="11" t="inlineStr">
@@ -55124,18 +55124,18 @@
       </c>
       <c r="Z22" s="11" t="inlineStr">
         <is>
-          <t>$36,500.00</t>
+          <t>$45,700.00</t>
         </is>
       </c>
       <c r="AA22" s="11" t="n"/>
       <c r="AB22" s="11" t="inlineStr">
         <is>
-          <t>$16.35</t>
+          <t>$20.48</t>
         </is>
       </c>
       <c r="AC22" s="11" t="inlineStr">
         <is>
-          <t>$24.53</t>
+          <t>$30.72</t>
         </is>
       </c>
       <c r="AD22" s="11" t="inlineStr">
@@ -55145,7 +55145,7 @@
       </c>
       <c r="AE22" s="11" t="inlineStr">
         <is>
-          <t>$1,400.00</t>
+          <t>$1,800.00</t>
         </is>
       </c>
       <c r="AF22" s="11" t="inlineStr">
@@ -55155,18 +55155,18 @@
       </c>
       <c r="AG22" s="11" t="inlineStr">
         <is>
-          <t>$35,400.00</t>
+          <t>$44,400.00</t>
         </is>
       </c>
       <c r="AH22" s="11" t="n"/>
       <c r="AI22" s="11" t="inlineStr">
         <is>
-          <t>$15.87</t>
+          <t>$19.90</t>
         </is>
       </c>
       <c r="AJ22" s="11" t="inlineStr">
         <is>
-          <t>$23.80</t>
+          <t>$29.85</t>
         </is>
       </c>
       <c r="AK22" s="11" t="inlineStr">
@@ -55176,7 +55176,7 @@
       </c>
       <c r="AL22" s="11" t="inlineStr">
         <is>
-          <t>$1,400.00</t>
+          <t>$1,700.00</t>
         </is>
       </c>
       <c r="AM22" s="11" t="inlineStr">
@@ -55186,18 +55186,18 @@
       </c>
       <c r="AN22" s="11" t="inlineStr">
         <is>
-          <t>$34,400.00</t>
+          <t>$43,100.00</t>
         </is>
       </c>
       <c r="AO22" s="11" t="n"/>
       <c r="AP22" s="11" t="inlineStr">
         <is>
-          <t>$15.43</t>
+          <t>$19.28</t>
         </is>
       </c>
       <c r="AQ22" s="11" t="inlineStr">
         <is>
-          <t>$23.14</t>
+          <t>$28.92</t>
         </is>
       </c>
       <c r="AR22" s="11" t="inlineStr">
@@ -55207,7 +55207,7 @@
       </c>
       <c r="AS22" s="11" t="inlineStr">
         <is>
-          <t>$1,300.00</t>
+          <t>$1,700.00</t>
         </is>
       </c>
       <c r="AT22" s="11" t="inlineStr">
@@ -55217,7 +55217,7 @@
       </c>
       <c r="AU22" s="11" t="inlineStr">
         <is>
-          <t>$33,400.00</t>
+          <t>$41,800.00</t>
         </is>
       </c>
       <c r="AV22" s="11" t="inlineStr">
@@ -62742,7 +62742,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-07-20 19:47 from the reference warehouse (public.ext_*)</t>
+          <t>generated 2026-07-21 18:05 from the reference warehouse (public.ext_*)</t>
         </is>
       </c>
     </row>

--- a/public/fixtures/edge_healthcare.xlsx
+++ b/public/fixtures/edge_healthcare.xlsx
@@ -53146,7 +53146,7 @@
       </c>
       <c r="B9" s="43" t="inlineStr">
         <is>
-          <t>07/21/2026</t>
+          <t>07/22/2026</t>
         </is>
       </c>
       <c r="C9" s="43" t="n"/>
@@ -53940,12 +53940,12 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>07/23/1992</t>
+          <t>10/10/1991</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -53965,7 +53965,7 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>19-4021</t>
+          <t>19-3051</t>
         </is>
       </c>
       <c r="H18" s="14" t="inlineStr">
@@ -53975,7 +53975,7 @@
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>Biological Technicians</t>
+          <t>Urban and Regional Planners</t>
         </is>
       </c>
       <c r="J18" s="14" t="inlineStr">
@@ -53985,7 +53985,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>07/10/2020</t>
+          <t>03/18/2016</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54013,12 +54013,12 @@
       <c r="R18" s="14" t="n"/>
       <c r="S18" s="14" t="inlineStr">
         <is>
-          <t>$14.57</t>
+          <t>$19.18</t>
         </is>
       </c>
       <c r="T18" s="13" t="inlineStr">
         <is>
-          <t>$21.86</t>
+          <t>$28.77</t>
         </is>
       </c>
       <c r="U18" s="11" t="inlineStr">
@@ -54038,7 +54038,7 @@
       </c>
       <c r="X18" s="11" t="inlineStr">
         <is>
-          <t>$1,300.00</t>
+          <t>$1,700.00</t>
         </is>
       </c>
       <c r="Y18" s="11" t="inlineStr">
@@ -54048,18 +54048,18 @@
       </c>
       <c r="Z18" s="11" t="inlineStr">
         <is>
-          <t>$31,600.00</t>
+          <t>$41,600.00</t>
         </is>
       </c>
       <c r="AA18" s="11" t="n"/>
       <c r="AB18" s="11" t="inlineStr">
         <is>
-          <t>$14.18</t>
+          <t>$18.65</t>
         </is>
       </c>
       <c r="AC18" s="11" t="inlineStr">
         <is>
-          <t>$21.27</t>
+          <t>$27.97</t>
         </is>
       </c>
       <c r="AD18" s="11" t="inlineStr">
@@ -54069,7 +54069,7 @@
       </c>
       <c r="AE18" s="11" t="inlineStr">
         <is>
-          <t>$1,200.00</t>
+          <t>$1,600.00</t>
         </is>
       </c>
       <c r="AF18" s="11" t="inlineStr">
@@ -54079,18 +54079,18 @@
       </c>
       <c r="AG18" s="11" t="inlineStr">
         <is>
-          <t>$30,700.00</t>
+          <t>$40,400.00</t>
         </is>
       </c>
       <c r="AH18" s="11" t="n"/>
       <c r="AI18" s="11" t="inlineStr">
         <is>
-          <t>$13.75</t>
+          <t>$18.08</t>
         </is>
       </c>
       <c r="AJ18" s="11" t="inlineStr">
         <is>
-          <t>$20.62</t>
+          <t>$27.12</t>
         </is>
       </c>
       <c r="AK18" s="11" t="inlineStr">
@@ -54100,7 +54100,7 @@
       </c>
       <c r="AL18" s="11" t="inlineStr">
         <is>
-          <t>$1,200.00</t>
+          <t>$1,600.00</t>
         </is>
       </c>
       <c r="AM18" s="11" t="inlineStr">
@@ -54110,18 +54110,18 @@
       </c>
       <c r="AN18" s="11" t="inlineStr">
         <is>
-          <t>$29,800.00</t>
+          <t>$39,200.00</t>
         </is>
       </c>
       <c r="AO18" s="11" t="n"/>
       <c r="AP18" s="11" t="inlineStr">
         <is>
-          <t>$13.32</t>
+          <t>$17.60</t>
         </is>
       </c>
       <c r="AQ18" s="11" t="inlineStr">
         <is>
-          <t>$19.98</t>
+          <t>$26.40</t>
         </is>
       </c>
       <c r="AR18" s="11" t="inlineStr">
@@ -54131,7 +54131,7 @@
       </c>
       <c r="AS18" s="11" t="inlineStr">
         <is>
-          <t>$1,200.00</t>
+          <t>$1,500.00</t>
         </is>
       </c>
       <c r="AT18" s="11" t="inlineStr">
@@ -54141,7 +54141,7 @@
       </c>
       <c r="AU18" s="11" t="inlineStr">
         <is>
-          <t>$28,900.00</t>
+          <t>$38,100.00</t>
         </is>
       </c>
       <c r="AV18" s="11" t="inlineStr">
@@ -54209,12 +54209,12 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>01/09/1990</t>
+          <t>10/02/1963</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -54234,7 +54234,7 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>19-3039</t>
+          <t>17-2112</t>
         </is>
       </c>
       <c r="H19" s="14" t="inlineStr">
@@ -54244,7 +54244,7 @@
       </c>
       <c r="I19" s="14" t="inlineStr">
         <is>
-          <t>Clinical Neuropsychologists</t>
+          <t>Industrial Engineers</t>
         </is>
       </c>
       <c r="J19" s="14" t="inlineStr">
@@ -54254,7 +54254,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>10/21/2012</t>
+          <t>04/16/2013</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54282,12 +54282,12 @@
       <c r="R19" s="14" t="n"/>
       <c r="S19" s="14" t="inlineStr">
         <is>
-          <t>$17.55</t>
+          <t>$27.16</t>
         </is>
       </c>
       <c r="T19" s="13" t="inlineStr">
         <is>
-          <t>$26.33</t>
+          <t>$40.74</t>
         </is>
       </c>
       <c r="U19" s="11" t="inlineStr">
@@ -54307,7 +54307,7 @@
       </c>
       <c r="X19" s="11" t="inlineStr">
         <is>
-          <t>$1,500.00</t>
+          <t>$2,400.00</t>
         </is>
       </c>
       <c r="Y19" s="11" t="inlineStr">
@@ -54317,18 +54317,18 @@
       </c>
       <c r="Z19" s="11" t="inlineStr">
         <is>
-          <t>$38,000.00</t>
+          <t>$58,900.00</t>
         </is>
       </c>
       <c r="AA19" s="11" t="n"/>
       <c r="AB19" s="11" t="inlineStr">
         <is>
-          <t>$17.02</t>
+          <t>$26.39</t>
         </is>
       </c>
       <c r="AC19" s="11" t="inlineStr">
         <is>
-          <t>$25.53</t>
+          <t>$39.59</t>
         </is>
       </c>
       <c r="AD19" s="11" t="inlineStr">
@@ -54338,7 +54338,7 @@
       </c>
       <c r="AE19" s="11" t="inlineStr">
         <is>
-          <t>$1,500.00</t>
+          <t>$2,300.00</t>
         </is>
       </c>
       <c r="AF19" s="11" t="inlineStr">
@@ -54348,18 +54348,18 @@
       </c>
       <c r="AG19" s="11" t="inlineStr">
         <is>
-          <t>$36,900.00</t>
+          <t>$57,200.00</t>
         </is>
       </c>
       <c r="AH19" s="11" t="n"/>
       <c r="AI19" s="11" t="inlineStr">
         <is>
-          <t>$16.54</t>
+          <t>$25.62</t>
         </is>
       </c>
       <c r="AJ19" s="11" t="inlineStr">
         <is>
-          <t>$24.81</t>
+          <t>$38.43</t>
         </is>
       </c>
       <c r="AK19" s="11" t="inlineStr">
@@ -54369,7 +54369,7 @@
       </c>
       <c r="AL19" s="11" t="inlineStr">
         <is>
-          <t>$1,400.00</t>
+          <t>$2,200.00</t>
         </is>
       </c>
       <c r="AM19" s="11" t="inlineStr">
@@ -54379,18 +54379,18 @@
       </c>
       <c r="AN19" s="11" t="inlineStr">
         <is>
-          <t>$35,800.00</t>
+          <t>$55,500.00</t>
         </is>
       </c>
       <c r="AO19" s="11" t="n"/>
       <c r="AP19" s="11" t="inlineStr">
         <is>
-          <t>$16.06</t>
+          <t>$24.86</t>
         </is>
       </c>
       <c r="AQ19" s="11" t="inlineStr">
         <is>
-          <t>$24.09</t>
+          <t>$37.29</t>
         </is>
       </c>
       <c r="AR19" s="11" t="inlineStr">
@@ -54400,7 +54400,7 @@
       </c>
       <c r="AS19" s="11" t="inlineStr">
         <is>
-          <t>$1,400.00</t>
+          <t>$2,200.00</t>
         </is>
       </c>
       <c r="AT19" s="11" t="inlineStr">
@@ -54410,7 +54410,7 @@
       </c>
       <c r="AU19" s="11" t="inlineStr">
         <is>
-          <t>$34,800.00</t>
+          <t>$53,900.00</t>
         </is>
       </c>
       <c r="AV19" s="11" t="inlineStr">
@@ -54478,12 +54478,12 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>08/20/1997</t>
+          <t>07/11/1964</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -54503,7 +54503,7 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>17-2121</t>
+          <t>15-2041</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
@@ -54513,7 +54513,7 @@
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>Marine Engineers and Naval Architects</t>
+          <t>Statisticians</t>
         </is>
       </c>
       <c r="J20" s="14" t="inlineStr">
@@ -54523,7 +54523,7 @@
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>02/03/2020</t>
+          <t>02/04/2020</t>
         </is>
       </c>
       <c r="L20" s="14" t="n"/>
@@ -54551,12 +54551,12 @@
       <c r="R20" s="14" t="n"/>
       <c r="S20" s="14" t="inlineStr">
         <is>
-          <t>$32.07</t>
+          <t>$23.17</t>
         </is>
       </c>
       <c r="T20" s="13" t="inlineStr">
         <is>
-          <t>$48.11</t>
+          <t>$34.76</t>
         </is>
       </c>
       <c r="U20" s="11" t="inlineStr">
@@ -54576,7 +54576,7 @@
       </c>
       <c r="X20" s="11" t="inlineStr">
         <is>
-          <t>$2,800.00</t>
+          <t>$2,000.00</t>
         </is>
       </c>
       <c r="Y20" s="11" t="inlineStr">
@@ -54586,18 +54586,18 @@
       </c>
       <c r="Z20" s="11" t="inlineStr">
         <is>
-          <t>$69,500.00</t>
+          <t>$50,200.00</t>
         </is>
       </c>
       <c r="AA20" s="11" t="n"/>
       <c r="AB20" s="11" t="inlineStr">
         <is>
-          <t>$31.15</t>
+          <t>$22.50</t>
         </is>
       </c>
       <c r="AC20" s="11" t="inlineStr">
         <is>
-          <t>$46.72</t>
+          <t>$33.75</t>
         </is>
       </c>
       <c r="AD20" s="11" t="inlineStr">
@@ -54607,7 +54607,7 @@
       </c>
       <c r="AE20" s="11" t="inlineStr">
         <is>
-          <t>$2,700.00</t>
+          <t>$1,900.00</t>
         </is>
       </c>
       <c r="AF20" s="11" t="inlineStr">
@@ -54617,18 +54617,18 @@
       </c>
       <c r="AG20" s="11" t="inlineStr">
         <is>
-          <t>$67,500.00</t>
+          <t>$48,700.00</t>
         </is>
       </c>
       <c r="AH20" s="11" t="n"/>
       <c r="AI20" s="11" t="inlineStr">
         <is>
-          <t>$30.24</t>
+          <t>$21.83</t>
         </is>
       </c>
       <c r="AJ20" s="11" t="inlineStr">
         <is>
-          <t>$45.36</t>
+          <t>$32.74</t>
         </is>
       </c>
       <c r="AK20" s="11" t="inlineStr">
@@ -54638,7 +54638,7 @@
       </c>
       <c r="AL20" s="11" t="inlineStr">
         <is>
-          <t>$2,600.00</t>
+          <t>$1,900.00</t>
         </is>
       </c>
       <c r="AM20" s="11" t="inlineStr">
@@ -54648,18 +54648,18 @@
       </c>
       <c r="AN20" s="11" t="inlineStr">
         <is>
-          <t>$65,500.00</t>
+          <t>$47,300.00</t>
         </is>
       </c>
       <c r="AO20" s="11" t="n"/>
       <c r="AP20" s="11" t="inlineStr">
         <is>
-          <t>$29.38</t>
+          <t>$21.20</t>
         </is>
       </c>
       <c r="AQ20" s="11" t="inlineStr">
         <is>
-          <t>$44.07</t>
+          <t>$31.80</t>
         </is>
       </c>
       <c r="AR20" s="11" t="inlineStr">
@@ -54669,7 +54669,7 @@
       </c>
       <c r="AS20" s="11" t="inlineStr">
         <is>
-          <t>$2,500.00</t>
+          <t>$1,800.00</t>
         </is>
       </c>
       <c r="AT20" s="11" t="inlineStr">
@@ -54679,7 +54679,7 @@
       </c>
       <c r="AU20" s="11" t="inlineStr">
         <is>
-          <t>$63,600.00</t>
+          <t>$45,900.00</t>
         </is>
       </c>
       <c r="AV20" s="11" t="inlineStr">
@@ -54747,12 +54747,12 @@
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>10/06/1995</t>
+          <t>07/15/1964</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -54772,7 +54772,7 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>15-2041</t>
+          <t>11-9179</t>
         </is>
       </c>
       <c r="H21" s="14" t="inlineStr">
@@ -54782,7 +54782,7 @@
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
-          <t>Biostatisticians</t>
+          <t>Fitness and Wellness Coordinators</t>
         </is>
       </c>
       <c r="J21" s="14" t="inlineStr">
@@ -54792,7 +54792,7 @@
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>09/21/2022</t>
+          <t>05/22/2017</t>
         </is>
       </c>
       <c r="L21" s="14" t="n"/>
@@ -54820,12 +54820,12 @@
       <c r="R21" s="14" t="n"/>
       <c r="S21" s="14" t="inlineStr">
         <is>
-          <t>$17.16</t>
+          <t>$11.92</t>
         </is>
       </c>
       <c r="T21" s="13" t="inlineStr">
         <is>
-          <t>$25.74</t>
+          <t>$17.88</t>
         </is>
       </c>
       <c r="U21" s="11" t="inlineStr">
@@ -54845,7 +54845,7 @@
       </c>
       <c r="X21" s="11" t="inlineStr">
         <is>
-          <t>$1,500.00</t>
+          <t>$1,000.00</t>
         </is>
       </c>
       <c r="Y21" s="11" t="inlineStr">
@@ -54855,18 +54855,18 @@
       </c>
       <c r="Z21" s="11" t="inlineStr">
         <is>
-          <t>$37,200.00</t>
+          <t>$25,800.00</t>
         </is>
       </c>
       <c r="AA21" s="11" t="n"/>
       <c r="AB21" s="11" t="inlineStr">
         <is>
-          <t>$16.68</t>
+          <t>$11.54</t>
         </is>
       </c>
       <c r="AC21" s="11" t="inlineStr">
         <is>
-          <t>$25.02</t>
+          <t>$17.31</t>
         </is>
       </c>
       <c r="AD21" s="11" t="inlineStr">
@@ -54876,7 +54876,7 @@
       </c>
       <c r="AE21" s="11" t="inlineStr">
         <is>
-          <t>$1,400.00</t>
+          <t>$1,000.00</t>
         </is>
       </c>
       <c r="AF21" s="11" t="inlineStr">
@@ -54886,18 +54886,18 @@
       </c>
       <c r="AG21" s="11" t="inlineStr">
         <is>
-          <t>$36,100.00</t>
+          <t>$25,000.00</t>
         </is>
       </c>
       <c r="AH21" s="11" t="n"/>
       <c r="AI21" s="11" t="inlineStr">
         <is>
-          <t>$16.15</t>
+          <t>$11.20</t>
         </is>
       </c>
       <c r="AJ21" s="11" t="inlineStr">
         <is>
-          <t>$24.22</t>
+          <t>$16.80</t>
         </is>
       </c>
       <c r="AK21" s="11" t="inlineStr">
@@ -54907,7 +54907,7 @@
       </c>
       <c r="AL21" s="11" t="inlineStr">
         <is>
-          <t>$1,400.00</t>
+          <t>$1,000.00</t>
         </is>
       </c>
       <c r="AM21" s="11" t="inlineStr">
@@ -54917,18 +54917,18 @@
       </c>
       <c r="AN21" s="11" t="inlineStr">
         <is>
-          <t>$35,000.00</t>
+          <t>$24,300.00</t>
         </is>
       </c>
       <c r="AO21" s="11" t="n"/>
       <c r="AP21" s="11" t="inlineStr">
         <is>
-          <t>$15.67</t>
+          <t>$10.91</t>
         </is>
       </c>
       <c r="AQ21" s="11" t="inlineStr">
         <is>
-          <t>$23.50</t>
+          <t>$16.37</t>
         </is>
       </c>
       <c r="AR21" s="11" t="inlineStr">
@@ -54938,7 +54938,7 @@
       </c>
       <c r="AS21" s="11" t="inlineStr">
         <is>
-          <t>$1,400.00</t>
+          <t>$900.00</t>
         </is>
       </c>
       <c r="AT21" s="11" t="inlineStr">
@@ -54948,7 +54948,7 @@
       </c>
       <c r="AU21" s="11" t="inlineStr">
         <is>
-          <t>$34,000.00</t>
+          <t>$23,600.00</t>
         </is>
       </c>
       <c r="AV21" s="11" t="inlineStr">
@@ -55016,7 +55016,7 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>11/19/2000</t>
+          <t>07/15/1992</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -55041,7 +55041,7 @@
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>11-9179</t>
+          <t>19-3099</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
@@ -55051,7 +55051,7 @@
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>Personal Service Managers, All Other</t>
+          <t>Transportation Planners</t>
         </is>
       </c>
       <c r="J22" s="14" t="inlineStr">
@@ -55061,7 +55061,7 @@
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>06/05/2019</t>
+          <t>11/03/2014</t>
         </is>
       </c>
       <c r="L22" s="14" t="n"/>
@@ -55089,12 +55089,12 @@
       <c r="R22" s="14" t="n"/>
       <c r="S22" s="14" t="inlineStr">
         <is>
-          <t>$21.11</t>
+          <t>$23.51</t>
         </is>
       </c>
       <c r="T22" s="13" t="inlineStr">
         <is>
-          <t>$31.66</t>
+          <t>$35.27</t>
         </is>
       </c>
       <c r="U22" s="11" t="inlineStr">
@@ -55114,7 +55114,7 @@
       </c>
       <c r="X22" s="11" t="inlineStr">
         <is>
-          <t>$1,800.00</t>
+          <t>$2,000.00</t>
         </is>
       </c>
       <c r="Y22" s="11" t="inlineStr">
@@ -55124,18 +55124,18 @@
       </c>
       <c r="Z22" s="11" t="inlineStr">
         <is>
-          <t>$45,700.00</t>
+          <t>$50,900.00</t>
         </is>
       </c>
       <c r="AA22" s="11" t="n"/>
       <c r="AB22" s="11" t="inlineStr">
         <is>
-          <t>$20.48</t>
+          <t>$22.79</t>
         </is>
       </c>
       <c r="AC22" s="11" t="inlineStr">
         <is>
-          <t>$30.72</t>
+          <t>$34.19</t>
         </is>
       </c>
       <c r="AD22" s="11" t="inlineStr">
@@ -55145,7 +55145,7 @@
       </c>
       <c r="AE22" s="11" t="inlineStr">
         <is>
-          <t>$1,800.00</t>
+          <t>$2,000.00</t>
         </is>
       </c>
       <c r="AF22" s="11" t="inlineStr">
@@ -55155,18 +55155,18 @@
       </c>
       <c r="AG22" s="11" t="inlineStr">
         <is>
-          <t>$44,400.00</t>
+          <t>$49,400.00</t>
         </is>
       </c>
       <c r="AH22" s="11" t="n"/>
       <c r="AI22" s="11" t="inlineStr">
         <is>
-          <t>$19.90</t>
+          <t>$22.16</t>
         </is>
       </c>
       <c r="AJ22" s="11" t="inlineStr">
         <is>
-          <t>$29.85</t>
+          <t>$33.24</t>
         </is>
       </c>
       <c r="AK22" s="11" t="inlineStr">
@@ -55176,7 +55176,7 @@
       </c>
       <c r="AL22" s="11" t="inlineStr">
         <is>
-          <t>$1,700.00</t>
+          <t>$1,900.00</t>
         </is>
       </c>
       <c r="AM22" s="11" t="inlineStr">
@@ -55186,18 +55186,18 @@
       </c>
       <c r="AN22" s="11" t="inlineStr">
         <is>
-          <t>$43,100.00</t>
+          <t>$48,000.00</t>
         </is>
       </c>
       <c r="AO22" s="11" t="n"/>
       <c r="AP22" s="11" t="inlineStr">
         <is>
-          <t>$19.28</t>
+          <t>$21.49</t>
         </is>
       </c>
       <c r="AQ22" s="11" t="inlineStr">
         <is>
-          <t>$28.92</t>
+          <t>$32.23</t>
         </is>
       </c>
       <c r="AR22" s="11" t="inlineStr">
@@ -55207,7 +55207,7 @@
       </c>
       <c r="AS22" s="11" t="inlineStr">
         <is>
-          <t>$1,700.00</t>
+          <t>$1,900.00</t>
         </is>
       </c>
       <c r="AT22" s="11" t="inlineStr">
@@ -55217,7 +55217,7 @@
       </c>
       <c r="AU22" s="11" t="inlineStr">
         <is>
-          <t>$41,800.00</t>
+          <t>$46,600.00</t>
         </is>
       </c>
       <c r="AV22" s="11" t="inlineStr">
@@ -62742,7 +62742,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-07-21 18:05 from the reference warehouse (public.ext_*)</t>
+          <t>generated 2026-07-22 14:39 from the reference warehouse (public.ext_*)</t>
         </is>
       </c>
     </row>
